--- a/colllege list.xlsx
+++ b/colllege list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2000137380\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743E0547-B331-4C90-905D-BE569DF68495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932E9A43-D7A3-4AF7-8C37-737015003B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" activeTab="1" xr2:uid="{91048C63-C892-4DA5-A1FD-1CE02FA725AE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="70">
   <si>
     <t>College</t>
   </si>
@@ -301,7 +301,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +317,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,9 +345,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1570,7 +1576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6B01F8-08A8-4AB3-B417-4E2D976F2E8B}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="111.5703125" bestFit="1" customWidth="1"/>
@@ -1700,7 +1706,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
@@ -1727,7 +1733,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
@@ -1781,7 +1787,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B23" t="s">
@@ -1792,7 +1798,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B24" t="s">
@@ -1819,7 +1825,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
@@ -1849,7 +1855,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B30" t="s">
@@ -1884,7 +1890,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B34" t="s">
@@ -1903,7 +1909,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B36" t="s">
@@ -1941,7 +1947,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B40" t="s">
@@ -1979,7 +1985,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B44" t="s">
@@ -2041,7 +2047,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B51" t="s">
@@ -2152,7 +2158,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B63" t="s">
@@ -2163,7 +2169,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B64" t="s">
@@ -2182,7 +2188,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B66" t="s">
@@ -2201,7 +2207,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="A68" t="s">
         <v>37</v>
       </c>
       <c r="B68" t="s">
@@ -2212,7 +2218,6 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
       <c r="B69" t="s">
         <v>2</v>
       </c>
@@ -2221,7 +2226,6 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="5"/>
       <c r="B70" t="s">
         <v>67</v>
       </c>
@@ -2230,7 +2234,6 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="5"/>
       <c r="B71" t="s">
         <v>66</v>
       </c>
@@ -2239,7 +2242,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B72" t="s">
@@ -2250,7 +2253,6 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="5"/>
       <c r="B73" t="s">
         <v>67</v>
       </c>
@@ -2259,7 +2261,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B74" t="s">
@@ -2270,7 +2272,6 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
       <c r="B75" t="s">
         <v>2</v>
       </c>
@@ -2279,7 +2280,6 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
       <c r="B76" t="s">
         <v>66</v>
       </c>
@@ -2288,7 +2288,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B77" t="s">
@@ -2299,7 +2299,6 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
       <c r="B78" t="s">
         <v>2</v>
       </c>
@@ -2308,7 +2307,6 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
       <c r="B79" t="s">
         <v>66</v>
       </c>
@@ -2317,7 +2315,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B80" t="s">
@@ -2328,7 +2326,6 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="5"/>
       <c r="B81" t="s">
         <v>2</v>
       </c>
@@ -2337,7 +2334,6 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="5"/>
       <c r="B82" t="s">
         <v>67</v>
       </c>
@@ -2346,7 +2342,6 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="5"/>
       <c r="B83" t="s">
         <v>66</v>
       </c>
@@ -2355,7 +2350,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
+      <c r="A84" t="s">
         <v>50</v>
       </c>
       <c r="B84" t="s">
@@ -2363,6 +2358,41 @@
       </c>
       <c r="C84">
         <v>82.37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>79.69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86">
+        <v>81.63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87">
+        <v>73.430000000000007</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88">
+        <v>77.53</v>
       </c>
     </row>
   </sheetData>
